--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.832</v>
+        <v>0.836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.836</v>
+        <v>0.839</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.267</v>
+        <v>1.3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.573</v>
+        <v>1.58</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提...</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publisher: 路透社（经环球网 / 新浪转载） Country/Jurisdiction: CN/VN/TH/IN Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用制造 Claim: 部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形</t>
+          <t>Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） Publisher: 新浪科技 / 中关村在线 Country/Jurisdiction: TW/CN/IN Publication date: 2025-07-03 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电子制造 Claim: 2025 年 7 月及 12 月，富士康两度要求/</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publisher: 路透社（经环球网 / 新浪转载） Country/Jurisdiction: CN/VN/TH/IN Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用制造 Claim: 部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -4277,12 +4277,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4367,15 +4367,15 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
+          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>东方财富网 / 腾讯新闻</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
+          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>澎湃新闻 / 盖世汽车社区</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ## </t>
+          <t xml:space="preserve">## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## </t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Market Access Risk; Trade Risk; Operational Risk ## </t>
+          <t xml:space="preserve">## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## </t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -12295,37 +12295,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_003; RELOC_006</t>
+          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_003; RETURN_004</t>
+          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.913</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1.2</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_004; RETURN_001; CASE_010; RELOC_005</t>
+          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_003; RELOC_005; WH_002</t>
+          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.76</v>
+        <v>1.813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.836</v>
+        <v>0.884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.913</v>
+        <v>0.92</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.699</v>
+        <v>0.82</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.839</v>
+        <v>0.902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3</v>
+        <v>1.467</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.58</v>
+        <v>1.647</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_005</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -822,17 +822,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>新易盛：2022年设立泰国基地，一二期已投产 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -867,14 +867,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -897,17 +897,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -972,17 +972,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） ...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 / 盖世汽车社区 Country/Jurisdiction: CN/VN Publication date: 2022-11-19 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 与 Vingroup 旗下 VinES 合资（国轩 51% / VinE</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_002 Title: 长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_002 Title: 长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） Publisher: 易车 / 证券之星（投资者互动平台） Country/Jurisdiction: CN/TH Publication date: 2025-05-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 整车/汽车 Claim: 在泰国罗勇府建设整车工厂，2025-05-16 竣工投产</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1102,7 +1102,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -1122,17 +1122,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_001 Title: 比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_001 Title: 比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网（转比亚迪官方） Country/Jurisdiction: CN/TH Publication date: 2024-07-04 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 整车/汽车 Claim: 2022-09 与 WHA 签约，在泰国罗勇府建全资乘用车工厂；2024-07-04 竣工投产，年</t>
+          <t>中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一份“炸裂”的半年业绩预告。 数据显示，中际旭创预计上半年实现归母净利润21. 5亿元-25亿元，增长幅度上限超300%，而业绩下限水平甚至已可比肩去年全年。 半年业绩或超去年全年 中际旭创业绩预告显示，该公司预计上半年实现净利润21. 5亿元-25亿元，同比增长250. 3%-307. 33%。 而且，中际旭创还称，今年上半年确认股权激励费用减少公司合并净利润约9300万元。 对于上半年业绩大幅增长，中际旭创解释</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1177,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1252,7 +1252,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -1272,27 +1272,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - Evidence ID: CASE_010 Title: 白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 Publisher: 美国白宫...</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: CASE_010 Title: 白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 Publisher: 美国白宫（经律所解读） Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 由WH_001与WH_002组成。对已在越南/泰国/马来西亚布局的企业，原产地举证</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -1347,35 +1347,35 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PLUS1_004</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar：China + 1 战略（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：硅片—电池—组件一体化产能以中国为核心。 主要市场：全球（中国、欧洲、美国...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>东方财富财富号</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：硅片—电池—组件一体化产能以中国为核心。 主要市场：全球（中国、欧洲、美国、新兴市场）。 供应链结构：硅料、硅片主要在中国，组件通过海外基地与出口进入欧美。 面临的问题：美国对东南亚四国光伏产品的双反与反规避调查，使'中国—东南亚—美国'路径的关税优势不稳定（参见 Task 1 的 CASE_002/CASE_003）。 ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对东南亚光伏组件的双反/反规避认定，以及美</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1467,14 +1467,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -1497,35 +1497,35 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - Evidence ID: CASE_010 Title: 白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 Publisher: 美国白宫...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_010 Title: 白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 Publisher: 美国白宫（经律所解读） Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 由WH_001与WH_002组成。对已在越南/泰国/马来西亚布局的企业，原产地举证</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1617,17 +1617,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_001 Title: 恩捷股份 Yunnan Energy New Material (Semcorp)...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1667,15 +1667,15 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_001 Title: 恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） Publisher: 恩捷股份公告（经东方财富网 / 央广网报道） Country/Jurisdiction: CN/MY Publication date: 2026-05-22 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电池材料 Claim: 2026</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1692,14 +1692,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 在AI算力基础设施持续扩张的背景下，具备高速率产品量产能力、全球化交付能力与核心器件自研能力的厂商，将在下一阶段竞争中占据主动。 对于下游客户而...</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1746,11 +1746,11 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>在AI算力基础设施持续扩张的背景下，具备高速率产品量产能力、全球化交付能力与核心器件自研能力的厂商，将在下一阶段竞争中占据主动。 对于下游客户而言，根据自身场景需求在“规模稳定”、“性价比”、“行业定制”三者之间做出选择，已成为当前光模块采购决策的关键。 C114中国通信网版权说明：凡注明来源为“C114通信网”的文章皆属C114版权所有，除与C114签署内容授权协议的单位外，其他单位未经允许禁止转载、摘编，违者必究。 如需使用，请联系021-54451141（汪先生）。 其中编译类仅出于传递更多信息之目的，系C114对海外相关站点最新信息的翻译稿，仅供</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1797,17 +1797,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） Publisher: 新浪科技 / 中关村在线 Country/Jurisdiction: TW/CN/IN Publication date: 2025-07-03 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电子制造 Claim: 2025 年 7 月及 12 月，富士康两度要求/</t>
+          <t>截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域发力。 公测版APP上线一周的下载量已超1000万。 未来，千问还将陆续接入电商、地图、本地生活等阿里业务生态场景。 在财报电话会上，阿里巴巴高管表示，目前看到客户对AI的需求非常旺盛，阿里云AI服务器上架节奏其实还是严重跟不上客户订单的增长速度，在手积压订单数量还在持续扩大。 8. 中国首个光量子计算机制造工厂！ 从“艺术品”到“工业品”蜕变 据C114报道，11月24日，“国际量子年大湾区活动周”主题活动——</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1872,17 +1872,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publisher: 路透社（经环球网 / 新浪转载） Country/Jurisdiction: CN/VN/TH/IN Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用制造 Claim: 部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形</t>
+          <t>截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域发力。 公测版APP上线一周的下载量已超1000万。 未来，千问还将陆续接入电商、地图、本地生活等阿里业务生态场景。 在财报电话会上，阿里巴巴高管表示，目前看到客户对AI的需求非常旺盛，阿里云AI服务器上架节奏其实还是严重跟不上客户订单的增长速度，在手积压订单数量还在持续扩大。 8. 中国首个光量子计算机制造工厂！ 从“艺术品”到“工业品”蜕变 据C114报道，11月24日，“国际量子年大湾区活动周”主题活动——</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一份“炸裂”的半年业绩预告。 数据显示，中际旭创预计上半年实现归母净利润21. 5亿元-25亿元，增长幅度上限超300%，而业绩下限水平甚至已可比肩去年全年。 半年业绩或超去年全年 中际旭创业绩预告显示，该公司预计上半年实现净利润21. 5亿元-25亿元，同比增长250. 3%-307. 33%。 而且，中际旭创还称，今年上半年确认股权激励费用减少公司合并净利润约9300万元。 对于上半年业绩大幅增长，中际旭创解释</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 在AI算力基础设施持续扩张的背景下，具备高速率产品量产能力、全球化交付能力与核心器件自研能力的厂商，将在下一阶段竞争中占据主动。 对于下游客户而...</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>在AI算力基础设施持续扩张的背景下，具备高速率产品量产能力、全球化交付能力与核心器件自研能力的厂商，将在下一阶段竞争中占据主动。 对于下游客户而言，根据自身场景需求在“规模稳定”、“性价比”、“行业定制”三者之间做出选择，已成为当前光模块采购决策的关键。 C114中国通信网版权说明：凡注明来源为“C114通信网”的文章皆属C114版权所有，除与C114签署内容授权协议的单位外，其他单位未经允许禁止转载、摘编，违者必究。 如需使用，请联系021-54451141（汪先生）。 其中编译类仅出于传递更多信息之目的，系C114对海外相关站点最新信息的翻译稿，仅供</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） ...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 / 盖世汽车社区 Country/Jurisdiction: CN/VN Publication date: 2022-11-19 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 与 Vingroup 旗下 VinES 合资（国轩 51% / VinE</t>
+          <t>玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向生产线”的关键一步，也为未来构建自主可控的量子产业链打下了坚实基础。 9. 谷歌TPU硬刚英伟达！ AI芯片市场从英伟达垄断转向多元化 据C114报道，当前全球AI大模型和芯片领域掀起新一轮军备竞赛。 美国白宫周一发布声明称，总统特朗普签署了一项行政命令，启动一项旨在利用AI变革科学研究方式、加速科学发现的全新国家计划“创世纪计划”。 在 AI大模型和芯片竞争背景下，对算力存在巨大需求。 谷歌近日发布了最新的大语</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_005</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2172,17 +2172,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>新易盛：2022年设立泰国基地，一二期已投产 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向生产线”的关键一步，也为未来构建自主可控的量子产业链打下了坚实基础。 9. 谷歌TPU硬刚英伟达！ AI芯片市场从英伟达垄断转向多元化 据C114报道，当前全球AI大模型和芯片领域掀起新一轮军备竞赛。 美国白宫周一发布声明称，总统特朗普签署了一项行政命令，启动一项旨在利用AI变革科学研究方式、加速科学发现的全新国家计划“创世纪计划”。 在 AI大模型和芯片竞争背景下，对算力存在巨大需求。 谷歌近日发布了最新的大语</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2217,17 +2217,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向生产线”的关键一步，也为未来构建自主可控的量子产业链打下了坚实基础。 9. 谷歌TPU硬刚英伟达！ AI芯片市场从英伟达垄断转向多元化 据C114报道，当前全球AI大模型和芯片领域掀起新一轮军备竞赛。 美国白宫周一发布声明称，总统特朗普签署了一项行政命令，启动一项旨在利用AI变革科学研究方式、加速科学发现的全新国家计划“创世纪计划”。 在 AI大模型和芯片竞争背景下，对算力存在巨大需求。 谷歌近日发布了最新的大语</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2517,17 +2517,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -2552,30 +2552,30 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2602,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2642,15 +2642,15 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -4277,17 +4277,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4296,11 +4296,11 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -4352,30 +4352,30 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4446,11 +4446,11 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4477,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -4502,30 +4502,30 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4742,15 +4742,15 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4767,17 +4767,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -4802,30 +4802,30 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research A...</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research Assistant Benin Institut de Recherche Empirique en Economie Politique - IREEP Leonard Wantchekon, President Stéphania Houngan, Research Associate Bolivia (Plurinational State of), Costa Rica, Dominican Republi</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4896,11 +4896,11 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5177,30 +5177,30 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_001 Title: 恩捷股份 Yunnan Energy New Material (Semcorp)...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_001 Title: 恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） Publisher: 恩捷股份公告（经东方财富网 / 央广网报道） Country/Jurisdiction: CN/MY Publication date: 2026-05-22 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 电池材料 Claim: 2026</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5271,11 +5271,11 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -5367,17 +5367,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -5402,30 +5402,30 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） Publisher: 36氪 / 财新网 Country/Jurisdiction: CN/DE Publication date: 2024-10-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5477,17 +5477,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5496,11 +5496,11 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5517,14 +5517,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
@@ -5552,30 +5552,30 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5627,30 +5627,30 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -6492,17 +6492,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
@@ -6527,30 +6527,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6577,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
@@ -6602,30 +6602,30 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6652,7 +6652,7 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
@@ -6677,30 +6677,30 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -6752,30 +6752,30 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -6942,17 +6942,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
@@ -6977,22 +6977,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7027,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市场：中国动力电池市场为主，海外客户（大众等）快速增加。 供应链结构：正极、负极、隔膜主要来自中国供应商，磷酸铁锂（LFP）技术路线自主。 面临的问题：整车客户在东南亚建厂后要求就近配套；纯从中国出口电池面临关税与交期风险，且越南本地无 LFP 电芯产能。 ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：越南 VinFast 本地化生产需要就近电池</t>
+          <t>35 Appendix Table 1: Leading exporters and importers in world merchandise trade, 2025 (Billion dollars and percentage) Rank Exporters Value Share Annual percentage change Rank Importers Value Share Annual percentage change 1 China 3,772 14. 4 5 1 United States of America 3,507 13</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7142,15 +7142,15 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
@@ -7197,35 +7197,35 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7252,7 +7252,7 @@
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
@@ -7272,35 +7272,35 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK +...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7317,14 +7317,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -7347,17 +7347,17 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publis...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7371,11 +7371,11 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publisher: 新浪财经 Country/Jurisdiction: CN/MY Publication date: 2026-02-06 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/储能 Claim: 在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -7422,35 +7422,35 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## </t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -7477,7 +7477,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
@@ -7497,17 +7497,17 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7517,15 +7517,15 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -7572,17 +7572,17 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7596,11 +7596,11 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网 / 腾讯新闻 Country/Jurisdiction: CN/VN Publication date: 2024-07-16 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池/消费电池 Claim: 2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -7617,14 +7617,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>KPMG_001</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -7647,17 +7647,17 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>毕马威（KPMG）</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7667,15 +7667,15 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher: 毕马威（KPMG） Country/Jurisdiction: US / Federal Publication date: 2026-05-01 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 通用 Key finding: 样本为462位年营收10亿美元以上企业的供应链负责人。样本是美国大企业，不代表</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -7692,14 +7692,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -7722,17 +7722,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7746,11 +7746,11 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。 ## 四、相关风险（Related Risk） 风险类</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -7777,7 +7777,7 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_001 Title: 比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7817,15 +7817,15 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_001 Title: 比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） Publisher: 东方财富网（转比亚迪官方） Country/Jurisdiction: CN/TH Publication date: 2024-07-04 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 整车/汽车 Claim: 2022-09 与 WHA 签约，在泰国罗勇府建全资乘用车工厂；2024-07-04 竣工投产，年</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -7872,35 +7872,35 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>宁德时代 CATL：China + 1 战略（多地区混合布局） - Evidence ID: PLUS1_001 Title: 宁德时代 CATL：China + 1 战略（多地区混合布局） Publisher:...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>每日经济新闻 / 搜狐网</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Evidence ID: PLUS1_001 Title: 宁德时代 CATL：China + 1 战略（多地区混合布局） Publisher: 每日经济新闻 / 搜狐网 Country/Jurisdiction: CN/HU Publication date: 2026-09-22 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在匈牙利德布勒森建设欧洲第二座电池工厂，投资约 73.4 亿欧元（匈牙利史上最大外资项目之一）</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -8177,17 +8177,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8196,11 +8196,11 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -8252,30 +8252,30 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8946,11 +8946,11 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -8967,17 +8967,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
@@ -9002,22 +9002,22 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK +...</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》 - -154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门...</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## 五、后续结果（Outcome） 成本影响：本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。</t>
+          <t>-154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门设计或制造的激 光器或激光系统。 在以激光为基础的浓缩过程中有重要 意义的激光器和激光部件包括《中华人 民共和国两用物项出口管制清单》中所 列的那些激光器和激光部件。激光系统 一般包含用于管理激光束（一个或多 个）和向同位素分离室发射激光束的光 学和电子部件。AVLIS 过程使用的激 光系统通常由两个激光器组成：一个铜 蒸气激光器或某些固体激光器和一个 可调染料激光器。MLIS使用的激光系 统通常由一个 CO2激</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -9642,17 +9642,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
@@ -9672,35 +9672,35 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华加征关税及客户'...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华加征关税及客户'中国+1'采购要求，推动消费类电芯产线外移。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威消费类锂电池工厂项目，投资总额不超过 20 亿元人民币；2026-08 公司表示越南消费类电芯生产基地预计 2026 年底投产。中国产能保留。 ## 四、相关风险（Related Risk） 风险</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -9717,17 +9717,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>5</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
@@ -9747,17 +9747,17 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9767,15 +9767,15 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">## 二、决策触发（Decision Trigger） 触发类型：market_access（市场准入） 触发细节：泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。 ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。 ## 四、相关风险（Related Risk） 风险类别：Trade Risk; Market Access Risk; Operational Risk ## </t>
+          <t>中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一份“炸裂”的半年业绩预告。 数据显示，中际旭创预计上半年实现归母净利润21. 5亿元-25亿元，增长幅度上限超300%，而业绩下限水平甚至已可比肩去年全年。 半年业绩或超去年全年 中际旭创业绩预告显示，该公司预计上半年实现净利润21. 5亿元-25亿元，同比增长250. 3%-307. 33%。 而且，中际旭创还称，今年上半年确认股权激励费用减少公司合并净利润约9300万元。 对于上半年业绩大幅增长，中际旭创解释</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -10392,17 +10392,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
@@ -10427,30 +10427,30 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -10467,17 +10467,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
@@ -10502,22 +10502,22 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="O134" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -11217,14 +11217,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>5</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
         <v>2</v>
@@ -11252,17 +11252,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -11367,14 +11367,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
@@ -11402,17 +11402,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -11442,14 +11442,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -11477,17 +11477,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -11496,11 +11496,11 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -11602,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11642,15 +11642,15 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -11847,22 +11847,22 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11871,11 +11871,11 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市场：中国 + 海外电池客户（含欧美）。 供应链结构：基膜与涂覆材料主要在中国生产，产品出口海外。 面临的问题：2024 年规划马来西亚隔膜项目（约 10 亿平方米/年、投资约 20 亿元）以求贴近海外客户并规避关税。 ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -11902,7 +11902,7 @@
         <v>2</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
@@ -11922,35 +11922,35 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: 澎湃新闻 Country/Jurisdiction: CN/TH Publication date: 2024-02-28 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 动力电池 Claim: 在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>5</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
@@ -11997,35 +11997,35 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18....</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O151" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18. 81亿-21. 50亿元，净利率高达37. 40%，盈利质量行业领先。 公司1. 6T光引擎实现规模化量产，布局CPO无源器件，深度绑定中际旭创、新易盛等头部厂商。 作为“卖铲人”定位，天孚通信在技术迭代中具备更强的抗风险能力。 三、第三梯队 7. 剑桥科技 剑桥科技2025年预计归母净利润2. 52亿-2. 78亿元，同比增长51%-67%。 800G LPO光模块通过客户验证，1. 6T产品进入Meta供应</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -12153,48 +12153,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_003; RELOC_002; RELOC_001</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.744</v>
+        <v>0.972</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12220,20 +12220,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_010</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; PLUS1_004; RELOC_004; RETURN_001</t>
+          <t>CASE_007; CASE_010</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -12243,25 +12243,25 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.732</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12287,48 +12287,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12354,48 +12354,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_004; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.913</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12429,37 +12429,37 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; DOC_001</t>
+          <t>CASE_002; CASE_003; CASE_010; DOC_001</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K6" t="n">
         <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.893</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1.8</v>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005</t>
+          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010</t>
+          <t>CASE_002; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -12779,25 +12779,25 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0.657</v>
+        <v>0.799</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -12831,40 +12831,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IMF_001; RETURN_001; CNGOV_001; RETURN_004; RELOC_004</t>
+          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="K12" t="n">
         <v>1.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.624</v>
+        <v>0.946</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -12965,40 +12965,40 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNCTAD_001; RETURN_004; IMF_001; RETURN_001; WTO_001</t>
+          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001</t>
+          <t>IMF_001; MCK_001; UNCTAD_001; WEF_001; WTO_001</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; RELOC_004; TRD_003</t>
+          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13181,25 +13181,25 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
         <v>1.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N17" t="n">
         <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.794</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -13233,40 +13233,40 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_003; WH_002</t>
+          <t>CASE_010; CSIS_001; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
         <v>1.8</v>
       </c>
       <c r="L18" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.865</v>
+        <v>0.989</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -13292,20 +13292,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_006; RELOC_004; RELOC_002; RETURN_001</t>
+          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -13315,25 +13315,25 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -13359,20 +13359,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RELOC_005; RETURN_001; RELOC_004; RELOC_001; PLUS1_001</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PLUS1_001; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -13382,22 +13382,22 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="O20" t="n">
-        <v>0.518</v>
+        <v>0.869</v>
       </c>
       <c r="P20" t="n">
         <v>1.4</v>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_001; WH_001</t>
+          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; RETURN_001; RELOC_006</t>
+          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13583,25 +13583,25 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K23" t="n">
         <v>1.8</v>
       </c>
       <c r="L23" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N23" t="n">
         <v>0.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0.792</v>
+        <v>0.84</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -13694,20 +13694,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; RELOC_005; RELOC_002</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_008</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; WH_002</t>
+          <t>CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -13717,22 +13717,22 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="O25" t="n">
-        <v>0.723</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>1.8</v>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; CASE_001</t>
+          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13866,7 +13866,7 @@
         <v>0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
       <c r="P27" t="n">
         <v>1.8</v>
@@ -13970,12 +13970,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; WH_002</t>
+          <t>CASE_002; CASE_003; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -13985,22 +13985,22 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M29" t="n">
         <v>0.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O29" t="n">
-        <v>0.743</v>
+        <v>0.83</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; UNCTAD_001; CNGOV_001; RETURN_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14067,10 +14067,10 @@
         <v>0.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0.655</v>
+        <v>0.699</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -14096,20 +14096,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RETURN_001; RELOC_006; WH_001</t>
+          <t>CASE_010; WH_002; WH_001; TRD_001; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CASE_010; RELOC_006; WH_002</t>
+          <t>CASE_007; CASE_010; TRD_001; WH_002</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -14119,22 +14119,22 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3</v>
+        <v>0.57</v>
       </c>
       <c r="O31" t="n">
-        <v>0.799</v>
+        <v>0.887</v>
       </c>
       <c r="P31" t="n">
         <v>1.8</v>

--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.82</v>
+        <v>0.829</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.902</v>
+        <v>0.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2721,11 +2721,11 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2796,11 +2796,11 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2817,14 +2817,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2871,11 +2871,11 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、海关总署 Country/Jurisdiction: CN / National Publication date: 2025-12-31 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 2026-01-01起实施，同时废止2024年第67号公告。用于判断产品是否属于中国侧</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2892,14 +2892,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2946,11 +2946,11 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3021,11 +3021,11 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、海关总署 Country/Jurisdiction: CN / National Publication date: 2025-12-31 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 2026-01-01起实施，同时废止2024年第67号公告。用于判断产品是否属于中国侧</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3171,11 +3171,11 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3246,11 +3246,11 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3696,11 +3696,11 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -3752,17 +3752,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3771,11 +3771,11 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3846,11 +3846,11 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3921,11 +3921,11 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4352,30 +4352,30 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4477,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -4502,30 +4502,30 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4592,15 +4592,15 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4667,15 +4667,15 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -4802,30 +4802,30 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research A...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research Assistant Benin Institut de Recherche Empirique en Economie Politique - IREEP Leonard Wantchekon, President Stéphania Houngan, Research Associate Bolivia (Plurinational State of), Costa Rica, Dominican Republi</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -4877,30 +4877,30 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Once leaders have defined their objectives, they can choose from a tool ...</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Once leaders have defined their objectives, they can choose from a tool kit of foresight development instruments. Below, we outline five that organizations frequently employ: — Horizon scanning: gathering internal and external perspectives to create a baseline understanding of th</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5346,11 +5346,11 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5421,11 +5421,11 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5567,15 +5567,15 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5642,15 +5642,15 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -6492,14 +6492,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -6527,30 +6527,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6602,30 +6602,30 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6696,11 +6696,11 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -6752,17 +6752,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6771,11 +6771,11 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -7017,14 +7017,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -7052,30 +7052,30 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>35 Appendix Table 1: Leading exporters and importers in world merchandise trade, 2025 (Billion dollars and percentage) Rank Exporters Value Share Annual percentage change Rank Importers Value Share Annual percentage change 1 China 3,772 14. 4 5 1 United States of America 3,507 13</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -7092,14 +7092,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7142,15 +7142,15 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -7202,30 +7202,30 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -7277,30 +7277,30 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -7392,17 +7392,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
@@ -7427,30 +7427,30 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -7467,17 +7467,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
@@ -7502,30 +7502,30 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -7767,17 +7767,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
@@ -7802,30 +7802,30 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -7877,30 +7877,30 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8046,11 +8046,11 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8121,11 +8121,11 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -8217,14 +8217,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
@@ -8252,30 +8252,30 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8946,11 +8946,11 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -8967,14 +8967,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -9002,17 +9002,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - -154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>-154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门设计或制造的激 光器或激光系统。 在以激光为基础的浓缩过程中有重要 意义的激光器和激光部件包括《中华人 民共和国两用物项出口管制清单》中所 列的那些激光器和激光部件。激光系统 一般包含用于管理激光束（一个或多 个）和向同位素分离室发射激光束的光 学和电子部件。AVLIS 过程使用的激 光系统通常由两个激光器组成：一个铜 蒸气激光器或某些固体激光器和一个 可调染料激光器。MLIS使用的激光系 统通常由一个 CO2激</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9096,11 +9096,11 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9171,11 +9171,11 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -9302,12 +9302,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9321,11 +9321,11 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9396,11 +9396,11 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10067,15 +10067,15 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -10092,14 +10092,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>5</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -10127,30 +10127,30 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -10296,11 +10296,11 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10371,11 +10371,11 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -10392,17 +10392,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
@@ -10427,30 +10427,30 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -10467,17 +10467,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
@@ -10502,22 +10502,22 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10596,11 +10596,11 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -10652,12 +10652,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10671,11 +10671,11 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -11027,17 +11027,17 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -11046,11 +11046,11 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -11067,14 +11067,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11121,11 +11121,11 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -11177,17 +11177,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11196,11 +11196,11 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -11252,17 +11252,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11271,11 +11271,11 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -11346,7 +11346,7 @@
         </is>
       </c>
       <c r="O142" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -11367,14 +11367,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
@@ -11402,17 +11402,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11421,11 +11421,11 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -11442,14 +11442,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -11477,30 +11477,30 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11567,15 +11567,15 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -11592,17 +11592,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C146" t="n">
         <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
@@ -11627,30 +11627,30 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2019-03-21 Effective da</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -11892,14 +11892,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>4</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -11927,30 +11927,30 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -12526,7 +12526,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.989</v>
+        <v>0.972</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12630,37 +12630,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009</t>
+          <t>BIS_001; BIS_002; CASE_009; FR_001</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K9" t="n">
         <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.893</v>
+        <v>0.989</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001</t>
+          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -12797,7 +12797,7 @@
         <v>0.799</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -12861,7 +12861,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.946</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>1.8</v>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003</t>
+          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13196,7 +13196,7 @@
         <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13263,7 +13263,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001</t>
+          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13330,7 +13330,7 @@
         <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="P19" t="n">
         <v>1.6</v>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -13397,7 +13397,7 @@
         <v>0.67</v>
       </c>
       <c r="O20" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
       <c r="P20" t="n">
         <v>1.4</v>
@@ -13434,12 +13434,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_003; WH_002</t>
+          <t>CASE_010; CSIS_001; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -13449,22 +13449,22 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.8</v>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.6</v>
-      </c>
       <c r="O21" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001</t>
+          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13583,22 +13583,22 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
         <v>1.8</v>
       </c>
       <c r="L23" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N23" t="n">
         <v>0.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0.84</v>
+        <v>0.792</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13769,37 +13769,37 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IMF_001; MCK_001; UNCTAD_001; WEF_001; WTO_001</t>
+          <t>IMF_001; MCK_001; UNCTAD_001; WTO_001</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0.869</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13866,7 +13866,7 @@
         <v>0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0.854</v>
+        <v>0.869</v>
       </c>
       <c r="P27" t="n">
         <v>1.8</v>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13970,12 +13970,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003</t>
+          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; TRD_003; WH_002</t>
+          <t>CASE_002; CASE_003; CASE_010; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -13985,22 +13985,22 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="O29" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001</t>
+          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14052,16 +14052,16 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N30" t="n">
         <v>0.6</v>
@@ -14070,7 +14070,7 @@
         <v>0.699</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -14104,12 +14104,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_001; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; TRD_001; WH_002</t>
+          <t>CASE_007; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -14119,22 +14119,22 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0.887</v>
+        <v>0.741</v>
       </c>
       <c r="P31" t="n">
         <v>1.8</v>

--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.813</v>
+        <v>1.85</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.884</v>
+        <v>0.796</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.913</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.829</v>
+        <v>0.826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9</v>
+        <v>0.843</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.467</v>
+        <v>1.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.647</v>
+        <v>1.395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS IMPROVEMENT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Note: 1 of 30 questions have &lt;3 expected evidence ids; a Top-5 average cannot exceed 1.2 with 1 gold doc or 1.4 with 2 gold docs.</t>
+          <t>Note: 9 of 40 questions have &lt;3 expected evidence ids; a Top-5 average cannot exceed 1.2 with 1 gold doc or 1.4 with 2 gold docs.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2517,14 +2517,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -2552,17 +2552,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2571,11 +2571,11 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -2627,30 +2627,30 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3246,11 +3246,11 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3342,14 +3342,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -3377,17 +3377,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3396,11 +3396,11 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3717,14 +3717,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -3752,17 +3752,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3771,11 +3771,11 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t xml:space="preserve">Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key </t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -4317,14 +4317,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -4352,17 +4352,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4371,11 +4371,11 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
@@ -4427,12 +4427,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4446,11 +4446,11 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4467,17 +4467,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -4502,30 +4502,30 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -4842,14 +4842,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
@@ -4877,30 +4877,30 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Once leaders have defined their objectives, they can choose from a tool ...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Once leaders have defined their objectives, they can choose from a tool kit of foresight development instruments. Below, we outline five that organizations frequently employ: — Horizon scanning: gathering internal and external perspectives to create a baseline understanding of th</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -4952,17 +4952,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4971,11 +4971,11 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5027,17 +5027,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5046,11 +5046,11 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -5102,12 +5102,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5117,15 +5117,15 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5142,14 +5142,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -5177,30 +5177,30 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5227,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -5252,30 +5252,30 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - 122 Indonesia Investments, Holding Company for Indonesia's State-Owned M...</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026/3/25 16:29 2026十大光模块厂商，光模块厂商有哪些 C114通信网 26 1 2026年，随着 AI 算力需求持续爆发与全球数据中心带宽升级加速，光模块行业迎来“800G普及+1. 6T放量”的双轮驱动阶段。 据行业预测，2026年全球800G光模块需求量有望突破4000万只，1. 6T需求亦进入商业化元年。 在这场高速光互联的竞逐中，中国光模块厂商凭借技术突破与产能优势占据全球主导地位。 本文综合</t>
+          <t>122 Indonesia Investments, Holding Company for Indonesia's State-Owned Miners Ready in Q1-2017. Viewed at: https://www. indonesia-investments. com/news/todays-headlines/holding-company-for-indonesia-s- state-owned-miners-ready-in-q1-2017/item7541; and Deloitte, 2019-20 Investment</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -6002,17 +6002,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6021,11 +6021,11 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t xml:space="preserve">Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key </t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -6492,14 +6492,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -6527,30 +6527,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -6602,30 +6602,30 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6696,11 +6696,11 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -6752,17 +6752,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6771,11 +6771,11 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7127,30 +7127,30 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>35 Appendix Table 1: Leading exporters and importers in world merchandise trade, 2025 (Billion dollars and percentage) Rank Exporters Value Share Annual percentage change Rank Importers Value Share Annual percentage change 1 China 3,772 14. 4 5 1 United States of America 3,507 13</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -7392,17 +7392,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
@@ -7427,30 +7427,30 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -7692,14 +7692,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -7727,12 +7727,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7742,15 +7742,15 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7896,11 +7896,11 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们调研发现，头部厂商在大陆和泰国加速扩产，预计2026年一季度将迎来产能集中释放，驱动业绩进入新一轮爬坡期。 【算力需求强劲，瓶颈在于供给】 算力产业链正处于高景气周期，AI模型持续创新演进推动算力需求快速增长。 业绩全面超预期： 谷歌新一代大模型Gemini 3表现优异，Scaling Law持续有效； 英伟达发布三季度财报，业绩及指引全面超预期。 谷歌与英伟达的强势表现，共同印证了模型创新与算力建设正在形成相互</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8046,11 +8046,11 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8117,15 +8117,15 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -8142,14 +8142,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -8177,30 +8177,30 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
@@ -8252,22 +8252,22 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -8517,14 +8517,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>2</v>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8571,11 +8571,11 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -8627,17 +8627,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8646,11 +8646,11 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8946,11 +8946,11 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -9002,17 +9002,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -9021,11 +9021,11 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -9302,12 +9302,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9321,11 +9321,11 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9396,11 +9396,11 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -10017,14 +10017,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -10052,30 +10052,30 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Evidence ID: MCK_001 Title: The art, science, and technology of geopolitical scenario planning Publisher: 麦肯锡（McKinsey） Country/Jurisdiction: 全球 Publication date: 2026-06-10 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 基于2026年2月对202</t>
+          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -10092,14 +10092,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WTO_003</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>5</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -10127,30 +10127,30 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2025-07 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: WTO国别</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -10392,17 +10392,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
@@ -10427,30 +10427,30 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -10467,17 +10467,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
@@ -10502,30 +10502,30 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10746,11 +10746,11 @@
         </is>
       </c>
       <c r="O134" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -10767,14 +10767,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>4</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
@@ -10802,12 +10802,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10821,11 +10821,11 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -10842,14 +10842,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>5</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -10877,30 +10877,30 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -11102,17 +11102,17 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -11121,11 +11121,11 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -11177,17 +11177,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11196,11 +11196,11 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11271,11 +11271,11 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -11346,7 +11346,7 @@
         </is>
       </c>
       <c r="O142" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -11421,11 +11421,11 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -11442,14 +11442,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -11477,30 +11477,30 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11567,15 +11567,15 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -11592,14 +11592,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C146" t="n">
         <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -11627,12 +11627,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11642,15 +11642,15 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2019-03-21 Effective da</t>
+          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -12029,6 +12029,3756 @@
         </is>
       </c>
       <c r="Q151" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
+        <v>49</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
+        <v>35</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
+        <v>34</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） Publisher: 美国贸易代表办公室（USTR，Federal Register） Country/Jurisdiction: US / Federal Publication date: 202</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>33</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>30</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NIO_001</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>60</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key </t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>XPEV_001</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>XPeng Inc. Form 20-F（fiscal year ended December 31, 2025）小鹏汽车2025财年年报 - Evidence ID: XPEV_001 Title: XPeng Inc. Form 20-F（fiscal year ended Dece...</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>58</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Evidence ID: XPEV_001 Title: XPeng Inc. Form 20-F（fiscal year ended December 31, 2025）小鹏汽车2025财年年报 Publisher: 小鹏汽车（XPeng Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-16 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>FR_001</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>美国国家档案馆联邦公报办公室</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>出口管制/关税</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>47</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>商务部</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>47</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ITA_001</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>5</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>美国国际贸易管理局（ITA）</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>47</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>48</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 Publisher: 雅保公司（Albemarle Corporation，SEC EDGAR） Country/Jurisdiction: US/CL/AU/CN / Federal (SEC registrant) Publication date: 2026-02-11 Status: CURRENT Topic: 供应链布局 Appli</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>32</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>30</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>28</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>5</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>28</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR）</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>47</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>33</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>战略与国际研究中心（CSIS）</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>33</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>29</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>5</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>29</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>WTO_002</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>44</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>WTO_003</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>37</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2025-07 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: WTO国别</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>32</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>4</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>32</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>5</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>31</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>41</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>36</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>36</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>4</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>34</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>5</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - After unwinding its joint venture with Ford and moving to sole operation...</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>31</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>After unwinding its joint venture with Ford and moving to sole operation of its Tennessee plant, the company is securing LFP materials for its North American ESS business and speeding up the search for demand beyond electric vehicles. Japan's Panasonic ranked sixth with 29. 7 GWh</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） - Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics i...</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>46</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） Publisher: 世界银行（World Bank） Country/Jurisdiction: 全球 / Global Publication date: 2023-04-28 Status: CURRENT Topic: 物流 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>32</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>31</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>30</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>5</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>26</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>63</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>39</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>39</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>4</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>39</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>5</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
+        <v>36</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>57</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
+        <v>34</v>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>2</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>28</v>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>4</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>2</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
+        <v>28</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>5</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>2</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O196" t="n">
+        <v>25</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR）</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O197" t="n">
+        <v>47</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） - Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics i...</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O198" t="n">
+        <v>39</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） Publisher: 世界银行（World Bank） Country/Jurisdiction: 全球 / Global Publication date: 2023-04-28 Status: CURRENT Topic: 物流 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O199" t="n">
+        <v>34</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O200" t="n">
+        <v>33</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>5</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O201" t="n">
+        <v>32</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -12045,7 +15795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12429,7 +16179,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_010</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -12444,25 +16194,25 @@
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
         <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -12563,7 +16313,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12578,22 +16328,22 @@
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
         <v>1.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0.952</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -12630,37 +16380,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; FR_001</t>
+          <t>BIS_001; BIS_002; CASE_009</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K9" t="n">
         <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0.989</v>
+        <v>0.893</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -12764,7 +16514,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001</t>
+          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -12779,25 +16529,25 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
       <c r="L11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M11" t="n">
         <v>0.8</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0.799</v>
+        <v>0.733</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -12831,7 +16581,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -12846,22 +16596,22 @@
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K12" t="n">
         <v>1.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.887</v>
       </c>
       <c r="P12" t="n">
         <v>1.8</v>
@@ -12898,7 +16648,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007</t>
+          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -12928,10 +16678,10 @@
         <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0.668</v>
+        <v>0.474</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -13032,7 +16782,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; NIO_001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -13166,7 +16916,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13181,22 +16931,22 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>1.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N17" t="n">
         <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.718</v>
+        <v>0.738</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -13233,7 +16983,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13300,12 +17050,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_008; TRD_003</t>
+          <t>CASE_002; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -13315,25 +17065,25 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.6</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -13367,12 +17117,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_008; KPMG_001</t>
+          <t>CASE_001; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -13382,22 +17132,22 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M20" t="n">
         <v>0.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0.854</v>
+        <v>0.741</v>
       </c>
       <c r="P20" t="n">
         <v>1.4</v>
@@ -13434,12 +17184,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001</t>
+          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; TRD_003; WH_002</t>
+          <t>CSIS_001; TRD_001; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -13464,7 +17214,7 @@
         <v>0.8</v>
       </c>
       <c r="O21" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -13501,37 +17251,37 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; CSIS_001; WH_001; WH_002</t>
+          <t>CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0.903</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -13568,7 +17318,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13635,7 +17385,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13769,12 +17519,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IMF_001; MCK_001; UNCTAD_001; WTO_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -13793,13 +17543,13 @@
         <v>0.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.869</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -13836,7 +17586,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001</t>
+          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13866,7 +17616,7 @@
         <v>0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
       <c r="P27" t="n">
         <v>1.8</v>
@@ -13903,7 +17653,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13933,7 +17683,7 @@
         <v>0.8</v>
       </c>
       <c r="O28" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -13970,7 +17720,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14037,7 +17787,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004</t>
+          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14052,22 +17802,22 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N30" t="n">
         <v>0.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0.699</v>
+        <v>0.616</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -14104,7 +17854,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -14140,6 +17890,676 @@
         <v>1.8</v>
       </c>
       <c r="Q31" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_002; TRD_001; DHS_001; EU_003</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; WTO_004</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>

--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.85</v>
+        <v>1.851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.796</v>
+        <v>0.78</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.826</v>
+        <v>0.838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.843</v>
+        <v>0.837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5</v>
+        <v>1.535</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.395</v>
+        <v>1.349</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Note: 9 of 40 questions have &lt;3 expected evidence ids; a Top-5 average cannot exceed 1.2 with 1 gold doc or 1.4 with 2 gold docs.</t>
+          <t>Note: 12 of 43 questions have &lt;3 expected evidence ids; a Top-5 average cannot exceed 1.2 with 1 gold doc or 1.4 with 2 gold docs.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2817,14 +2817,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2871,11 +2871,11 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2892,14 +2892,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2946,11 +2946,11 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -6642,14 +6642,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -6677,30 +6677,30 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -6752,30 +6752,30 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: ◆随产业 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: HS 851762仅为光</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -15117,14 +15117,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C193" t="n">
         <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" t="n">
         <v>2</v>
@@ -15152,22 +15152,22 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -15227,17 +15227,17 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -15246,11 +15246,11 @@
         </is>
       </c>
       <c r="O194" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -15302,17 +15302,17 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -15377,17 +15377,17 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -15396,11 +15396,11 @@
         </is>
       </c>
       <c r="O196" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -15779,6 +15779,1131 @@
         </is>
       </c>
       <c r="Q201" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O202" t="n">
+        <v>60</v>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O203" t="n">
+        <v>38</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O204" t="n">
+        <v>34</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>战略与国际研究中心（CSIS）</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O205" t="n">
+        <v>31</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The EV battery example shows the problem that a product passport is designed to solve. At its simplest, a product passport is a digital record that travels with a good through its supply chain, showing where its inputs came from and whether it qualiﬁes for preferential treatment </t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>5</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O206" t="n">
+        <v>30</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O207" t="n">
+        <v>60</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O208" t="n">
+        <v>33</v>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>2</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O209" t="n">
+        <v>31</v>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>4</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="O210" t="n">
+        <v>29</v>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>5</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O211" t="n">
+        <v>28</v>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） Publisher: SNE Research Country/Jurisdiction: 全球 / Global Publication date: 2026-10-02 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL </t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EU_002</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O212" t="n">
+        <v>50</v>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2024-05-03 E</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O213" t="n">
+        <v>49</v>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2019-03-21 Effective da</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>3</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O214" t="n">
+        <v>38</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>4</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O215" t="n">
+        <v>35</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） Publisher: 欧洲议会与欧盟理事会（EUR-Lex / Official Journal） Country/Jurisdiction: EU / EU-wide Publication date: 2023-07-28 Effective date: 2023-08-17 Status: CURRENT Topic: 市场准入 Appli</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>5</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O216" t="n">
+        <v>33</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） Publisher: 欧盟委员会（EUR-Lex / Official Journal） Country/Jurisdiction: EU/CN / EU-wide</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -15795,7 +16920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16246,7 +17371,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -16276,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.972</v>
+        <v>0.989</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -16916,7 +18041,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001</t>
+          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -16946,7 +18071,7 @@
         <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.738</v>
+        <v>0.732</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -18457,7 +19582,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001</t>
+          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -18472,22 +19597,22 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K40" t="n">
         <v>1.4</v>
       </c>
       <c r="L40" t="n">
-        <v>0.286</v>
+        <v>0.429</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N40" t="n">
         <v>0.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0.483</v>
+        <v>0.585</v>
       </c>
       <c r="P40" t="n">
         <v>1.8</v>
@@ -18560,6 +19685,207 @@
         <v>2</v>
       </c>
       <c r="Q41" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; DHS_001; EU_001; EU_003</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>

--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.837</v>
+        <v>0.834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.349</v>
+        <v>1.344</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NIO_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key </t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -6096,11 +6096,11 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Uncertai</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6171,11 +6171,11 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -6527,30 +6527,30 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -6602,30 +6602,30 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6752,30 +6752,30 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆光伏 Key finding: HS 2022版起光伏组件编码调整（旧</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -6846,11 +6846,11 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7971,11 +7971,11 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8421,11 +8421,11 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -10521,11 +10521,11 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Uncertai</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -10877,22 +10877,22 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） Publisher: 美国白宫 Country/Jurisdiction: US / Federal Publication date: 2026-06-03 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 收紧进口商资质、保证</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -10971,11 +10971,11 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否依赖中国中间</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -11177,17 +11177,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -11252,17 +11252,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11271,11 +11271,11 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -12602,17 +12602,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Bulk datab</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -12677,17 +12677,17 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t>Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档案馆联邦公报办公室 Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制/关税 Applicability scope: GENERAL Related industries: 通用 Key finding: 免费，无需key；按机构（BIS/USTR/CBP）过滤。 Uncertai</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -12771,11 +12771,11 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 持续更新（每日） Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索。</t>
+          <t>Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Publisher: 美国国际贸易管理局（ITA） Country/Jurisdiction: US / Federal Publication date: 2026-09-27 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 合并商务部、国务院、财政部11份清单；支持模糊名称搜索</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -15117,14 +15117,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C193" t="n">
         <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
         <v>2</v>
@@ -15152,22 +15152,22 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -15192,14 +15192,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C194" t="n">
         <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
         <v>2</v>
@@ -15227,30 +15227,30 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O194" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 持续更新 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 851762仅为光模块</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; ITA_001</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002</t>
+          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -18071,7 +18071,7 @@
         <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.732</v>
+        <v>0.678</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -18190,22 +18190,22 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N19" t="n">
         <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0.766</v>
+        <v>0.723</v>
       </c>
       <c r="P19" t="n">
         <v>1.8</v>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -19612,7 +19612,7 @@
         <v>0.5</v>
       </c>
       <c r="O40" t="n">
-        <v>0.585</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="P40" t="n">
         <v>1.8</v>

--- a/Task2_交付物/retrieval_results.xlsx
+++ b/Task2_交付物/retrieval_results.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.851</v>
+        <v>1.86</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.778</v>
+        <v>0.758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.772</v>
+        <v>0.767</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.838</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.834</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.535</v>
+        <v>1.465</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.344</v>
+        <v>1.316</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1371,11 +1371,11 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1446,11 +1446,11 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1467,14 +1467,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -1502,30 +1502,30 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 8. 中资企业在马开展投资合作应注意的问题 8.1 主要风险 （1）政治风险 相较于东南亚许多国家政权变动频繁、社会动荡、民族宗教问题突出、受恐...</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
+          <t>8. 中资企业在马开展投资合作应注意的问题 8.1 主要风险 （1）政治风险 相较于东南亚许多国家政权变动频繁、社会动荡、民族宗教问题突出、受恐怖主义 威胁，马来西亚政治风险较低，但也存在潜在的政治风险，包括逐渐激烈的党派之争、 美国对马来西亚的影响等。马来西亚实行多党制，由几个政党联合组成政党联盟执政， 虽然马来西亚政局总体平稳发展，但近年来政治斗争不断加剧。执政党、反对党和公民 社会三方的良性互动是马来西亚局势稳定的关键。 （2）环境保护风险 马来西亚目前没有统一的环保法典，环保法律体系相对复杂，由众多法律、法规、 条例组成。在一项可能对环境造成影响</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2592,17 +2592,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -2627,30 +2627,30 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2721,11 +2721,11 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2871,11 +2871,11 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
+          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -4017,14 +4017,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
@@ -4052,30 +4052,30 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4092,14 +4092,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -4127,22 +4127,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -4542,14 +4542,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
@@ -4577,12 +4577,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4596,11 +4596,11 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健 全海外综合服务体系，促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚 持统筹发展和安全，鼓励和支持有实力、信誉好、有国际竞争力的企业开展产供链国际 合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复 杂激烈，单边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的 新一代技术革命和产业变革深入发展，为国际经贸合作注入新动能、创造新</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -4652,12 +4652,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4667,15 +4667,15 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健全海外综合服务体系， 促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚持统筹发展和安全，鼓励和支持有 实力、信誉好、有国际竞争力的企业开展产供链国际合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复杂激烈，单 边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的新一代技术革命和产业 变革深入发展，为国际经贸合作注入新动能、创造新模</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4692,14 +4692,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4742,15 +4742,15 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Evidence ID: UNCTAD_001 Title: World Investment Report 2026: International Investment in a Turbulent Era Publisher: 联合国贸易和发展会议（UNCTAD） Country/Jurisdiction: 全球 Publication date: 2026-07-07 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industries: 通用 Key finding</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健 全海外综合服务体系，促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚 持统筹发展和安全，鼓励和支持有实力、信誉好、有国际竞争力的企业开展产供链国际 合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复 杂激烈，单边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的 新一代技术革命和产业变革深入发展，为国际经贸合作注入新动能、创造新</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4767,17 +4767,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -4802,30 +4802,30 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t>中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现予公布，⾃2026年7⽉1⽇起施⾏。 总 理 李 强 2026年5⽉5⽇ 国务院关于对外投资的规定国务院关于对外投资的规定 第⼀条第⼀条 为了推进⾼⽔平对外开放，促进对外投资⾼质量发展，有效实施对外投资管理，保护投资者及其对外投资合法权益，维护国家主权、安全、发展利益，根据《中华⼈⺠共和国对外关系法》、《中华⼈⺠共和国对外贸易法》等法律，制定本规定。第⼆条第⼆条 中华⼈⺠共和国境内（以下简称中国境内）投资者对外投</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
@@ -4877,17 +4877,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4896,11 +4896,11 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健 全海外综合服务体系，促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚 持统筹发展和安全，鼓励和支持有实力、信誉好、有国际竞争力的企业开展产供链国际 合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复 杂激烈，单边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的 新一代技术革命和产业变革深入发展，为国际经贸合作注入新动能、创造新</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -4952,17 +4952,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4971,11 +4971,11 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
+          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4992,14 +4992,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Publisher: 世界经济论坛（WEF） Country/Jurisdiction: 全球 Publication date: 2026-01-14 Status: CURRENT Topic: 宏观风险 Applicability scope: GENERAL Related industries: 通用 Key finding: 地缘经济对抗列为2026年首要风险。仅作PPT背景。</t>
+          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -5102,12 +5102,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 4. 投资环境 4.1 投资吸引力 【主要优势】越南吸引外资的主要优势：一是政局稳定，经济发展较快。越南政 府执政能力较强，政策具有连续性，注重...</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5117,15 +5117,15 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
+          <t>4. 投资环境 4.1 投资吸引力 【主要优势】越南吸引外资的主要优势：一是政局稳定，经济发展较快。越南政 府执政能力较强，政策具有连续性，注重经济建设和改善民生；二是劳动力成本 相对 较低；三是地理位置优越，位于中南半岛东部，海岸线长达 3260公里，港口众多，运 输便利。北部与中国接壤，凭借地理优势与中国保持产业链和供应链深度融合；四是 政策法规相对宽松，为外国投资者提供较全面的法律保障和较大力度的优惠政策；五 是对外开放程度较高，已签署17项自贸协定，另有2项自贸协定谈判正在推进中，投资 者可利用RCEP、中国—东盟自贸区等平台开拓更广阔的国际市场</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5142,14 +5142,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5192,15 +5192,15 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领域服务资源，为投资者提供服务保障。 省级以上⼈⺠政府及其有关部⻔提升公共服务能⼒和⽔平，为投资者提供法律法规、政策措施、投资指南、知识产权、⻛险防范应对、权益保护等⽅⾯的公共产品和服务。 第七条第七条 ⽀持咨询评估、法律服务、会计审计、信⽤评级、调解仲裁、知识产权等专业服务机构拓展海外服务⽹络，提⾼国际化服务能⼒和⽔平，为投资者及其对外投资提供⾼质量专业服务。 有关专业服务机构应当遵循诚实守信、勤勉尽责、独⽴客观</t>
+          <t>China remained the fourth largest destination for FDI in 2025, with trends indicating a transition from rapid expansion to more selective and strategic investment. Source: UNCTAD, based on information from the Ministry of Commerce, People’s Republic of China. a. Xinyi Li, An open</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5217,14 +5217,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -5252,30 +5252,30 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - 122 Indonesia Investments, Holding Company for Indonesia's State-Owned M...</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版） - 泰国（2025 年版） 寄语 泰国位于东盟中心位置，区位优势明显，社会总体较为稳定，政策透明度和贸易自 由化程度较高， 法律法规较为健全， 营商...</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>122 Indonesia Investments, Holding Company for Indonesia's State-Owned Miners Ready in Q1-2017. Viewed at: https://www. indonesia-investments. com/news/todays-headlines/holding-company-for-indonesia-s- state-owned-miners-ready-in-q1-2017/item7541; and Deloitte, 2019-20 Investment</t>
+          <t>泰国（2025 年版） 寄语 泰国位于东盟中心位置，区位优势明显，社会总体较为稳定，政策透明度和贸易自 由化程度较高， 法律法规较为健全， 营商环境开放包容，2024年泰国国内生产总值为5263 亿美元，是东盟第三大经济体。 泰国商品在东盟国家享受零关税待遇，对周边国家具有 较强辐射能力。 泰国投资促进政策以“泰国4. 0”战略为核心，重点支持发展新型汽车、智能电子、 农业与生物科技、食品加工、高端旅游和康养、自动化、航空与物流、综合医疗、生物 燃料和化学工业、数字经济、国防工业、人力教育等12大目标产业。 近年来，为增强产 供链韧性、 应对国际贸易挑战</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6396,11 +6396,11 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL </t>
+          <t xml:space="preserve">Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key </t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6527,17 +6527,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -6602,30 +6602,30 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
+          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -6677,22 +6677,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: CN / National Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: ◆电子/光电 Key finding: 看东南亚产能是否</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7521,11 +7521,11 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健全海外综合服务体系， 促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚持统筹发展和安全，鼓励和支持有 实力、信誉好、有国际竞争力的企业开展产供链国际合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复杂激烈，单 边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的新一代技术革命和产业 变革深入发展，为国际经贸合作注入新动能、创造新模</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -7767,17 +7767,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
@@ -7802,30 +7802,30 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 马来西亚/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 与CASE_002构成对照：同一规则下，供应链结构不同导致</t>
+          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7892,15 +7892,15 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publisher: 中国基金报 Country/Jurisdiction: CN / National Publication date: 2024-07-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 光模块 Key finding: 文中引用中际旭创互动平台回复，可据此到互动易查原始问答，升级为一手证据。</t>
+          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -8142,14 +8142,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
+          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
@@ -8252,12 +8252,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8271,11 +8271,11 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>The total decline in the value of exports to the United States in 2025 was about US$ 105 billion, while the increase to other destinations was almost three times as high at US$ 301 billion. These statistics suggest that more than just trade diversion is at play. Excess capacity i</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8417,15 +8417,15 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
+          <t>审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由文件以及支持重大转型决定的书面法律分析。 当基础生产事实不支持申报的原产地时，仅依赖供应商认证可能不足以应对。 进口商还应评估事先披露、裁定请求、修订原产地分析或加强供应商尽职调查是否适合高风险供应链。 主要要点 报告中的五项独立估计显示，每年非法转运资金流动在400亿至3030亿美元之间，关税收入损失每年达数百亿美元，收入回收潜力足以确保持续的执法关注。 行政命令14411的进口登记、保证和所有权披露要求将在入</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8442,14 +8442,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>2</v>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -8517,14 +8517,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
         <v>2</v>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
+          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8796,11 +8796,11 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
+          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
         <v>2</v>
@@ -8852,17 +8852,17 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-09-30 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 通用 Key finding: 政策事件型案例，由BIS_001和BIS_002组成。可用</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -8892,14 +8892,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
         <v>2</v>
@@ -8927,17 +8927,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8946,11 +8946,11 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） Publisher: 美国商务部工业与安全局（BIS） Country/Jurisdiction: US / Federal Publication date: 2025-11-12 Status: CURRENT Topic: 出口管制 Applicability scope: GEN</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9096,11 +9096,11 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9171,11 +9171,11 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9396,11 +9396,11 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿美元至3030亿美元之间，并宣布扩大使用分析和人工智能工具以识别虚假原产地索赔。 结合行政命令14411收紧的进口商问责要求，依赖供应商声明却未能证明实质性转变发生地点的进口商面临更多关税、处罚、拘留、EAPA行动及可能的刑事执法举报风险。 什么是转运？ 转运通常指通过中介国转运货物，以隐藏其真实产地并获得更优惠的关税待遇。 合法的供应链可能涉及多个国家，但当货物仅被重新标记、重新包装、重新开票、进行轻微加工，或</t>
+          <t>Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） Publisher: 美国贸易代表办公室（USTR） Country/Jurisdiction: US/MX/CA / Free trade area (USMCA) Publication date: 2020-07-01 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key fin</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -9846,7 +9846,7 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -10017,14 +10017,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -10052,30 +10052,30 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 4. 投资环境 4.1 投资吸引力 马来西亚政府欢迎和鼓励外国投资者对其制造业及相关服务业进行投资，近年来一 直致力于改善投资环境、完善投资法律...</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2020-11-25 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 </t>
+          <t>4. 投资环境 4.1 投资吸引力 马来西亚政府欢迎和鼓励外国投资者对其制造业及相关服务业进行投资，近年来一 直致力于改善投资环境、完善投资法律、加强投资激励，以吸引外资进入马来西亚的相 关行业。由于马来西亚投资法律体系完备、与国际通行标准接轨、各行业操作流程较为 规范，加之其独特的地缘优势，吸引了包括中国在内的各国企业赴马来西亚投资经营。 马来西亚投资环境的竞争优势主要体现在五个方面：地理位置优越，位于东南亚核 心地带，可成为进入东盟市场和前往中东澳新的桥梁；经济基础稳固，经济增长前景较 好；原材料资源丰富；人力资源素质较高，工资成本较低；民族关系融洽</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -10092,14 +10092,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WTO_003</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>5</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -10127,30 +10127,30 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: IN / National Publication date: 2025-07 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: WTO国别</t>
+          <t>商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管理，健全海外综合服务体系， 促进贸易投资一体化，引导产业链供应链合理有序跨境布局。 坚持统筹发展和安全，鼓励和支持有 实力、信誉好、有国际竞争力的企业开展产供链国际合作，持续提升跨国经营能力。 当前，世界百年未有之大变局加速演进，国际力量对比深刻调整，大国博弈更加复杂激烈，单 边主义、保护主义抬头，经济全球化遭遇逆流。 同时，以人工智能为代表的新一代技术革命和产业 变革深入发展，为国际经贸合作注入新动能、创造新模</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -10296,7 +10296,7 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -10392,17 +10392,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>4</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
@@ -10427,22 +10427,22 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publisher: 路透社（Reuters） Country/Jurisdiction: CN / National Publication date: 2026-09-14 Status: CURRENT Topic: 供应链布局 Applicability scope: GENERAL Related industries: 金属铸造 Key finding: 路透原文《Companies left China to do</t>
+          <t xml:space="preserve">Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 Publisher: 蔚来（NIO Inc.，SEC EDGAR） Country/Jurisdiction: CN / National Publication date: 2026-04-10 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 整车/汽车 Key </t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -10521,7 +10521,7 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -11142,14 +11142,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
@@ -11177,17 +11177,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
+          <t>Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） Publisher: 美国商务部 Country/Jurisdiction: US / Federal Publication date: 2023-08-23 Status: CURRENT Topic: 反规避 Applicabi</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -11252,17 +11252,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Importers and consumers of solar panels should review their supply chains and make any needed adjustments prior to June 2024 to ensure importers are not sourcing from these companies. U.S. companies should also evaluate the risks posed by these determinations when assessing produ</t>
+          <t>进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格的审查。 这些事实模式可能引发信息请求、货物搁置、审计查询、EAPA指控或罚款调查。 新的检测工具和执法能力 CBP及其他机构越来越多地拥有先进的数据工具，使转运更容易被识别。 报告描述了一个人工智能驱动的执法平台“侦探边境”，集成了进口数据分析、供应链地图、路由历史、所有权和关联分析、贸易流异常、产能比较以及计算机视觉，以识别高风险货物和潜在的虚假原产地索赔。 CBP的执法行动已经加快。 报告指出，自2025年</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -11292,14 +11292,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
+          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -11442,14 +11442,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -11477,17 +11477,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -11496,11 +11496,11 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版） Publisher: 世界贸易组织（WTO） Country/Jurisdiction: 全球 Publication date: 2026-03 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 通用 Key finding: 基准情景下2026年货物贸易量增速由2025年的4.6%放缓至1.9%。 Glo</t>
+          <t>Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment Publisher: 国际货币基金组织（IMF） Country/Jurisdiction: 全球 Publication date: 2023-04 Status: CURRENT Topic: 对外投资 Applicability scope: GENERAL Related industri</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -11892,14 +11892,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>4</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -11927,22 +11927,22 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O150" t="n">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Publisher: 战略与国际研究中心（CSIS） Country/Jurisdiction: US / Federal Publication date: 2026-08-04 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key find</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="O152" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="O153" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         </is>
       </c>
       <c r="O158" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="O160" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -13052,22 +13052,22 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O165" t="n">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） Publisher: 美国白宫贸易与制造业政策办公室 Country/Jurisdiction: US / Federal Publication date: 2026-08-13 Status: CURRENT Topic: 原产地与转运 Applicability scope: GENERAL Related industries: 通用 Key finding: 点名40</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -13092,14 +13092,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>2</v>
@@ -13127,22 +13127,22 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - _x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appe...</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O166" t="n">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
+          <t>_x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appellate Body Report, United States – Final Countervailing Duty Determination with Respect to Certain Softwood Lumber from Canada , WT/DS257/AB/R, para. 102. See recital (492), and in particular footnote 72, whi</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -13221,7 +13221,7 @@
         </is>
       </c>
       <c r="O167" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P172" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="O173" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -13727,17 +13727,17 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13746,11 +13746,11 @@
         </is>
       </c>
       <c r="O174" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -13817,15 +13817,15 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O175" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -13877,30 +13877,30 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O176" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -13971,7 +13971,7 @@
         </is>
       </c>
       <c r="O177" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P177" t="inlineStr">
         <is>
@@ -13992,14 +13992,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>2</v>
@@ -14027,17 +14027,17 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -14046,11 +14046,11 @@
         </is>
       </c>
       <c r="O178" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -14067,14 +14067,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -14102,17 +14102,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -14121,11 +14121,11 @@
         </is>
       </c>
       <c r="O179" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） Publisher: 美国财政部/国税局（Federal Register） Country/Jurisdiction: US / Federal Publication date: 20</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="O180" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
@@ -14217,17 +14217,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>5</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
@@ -14252,30 +14252,30 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - After unwinding its joint venture with Ford and moving to sole operation...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 庭和企业安装屋顶太阳能， 多余电力可售回电网； 能源效率提升， 工业节能， 目标到2040 年工业能耗降低11%，建筑节能，推广绿色建筑标准（如...</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O181" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>After unwinding its joint venture with Ford and moving to sole operation of its Tennessee plant, the company is securing LFP materials for its North American ESS business and speeding up the search for demand beyond electric vehicles. Japan's Panasonic ranked sixth with 29. 7 GWh</t>
+          <t>庭和企业安装屋顶太阳能， 多余电力可售回电网； 能源效率提升， 工业节能， 目标到2040 年工业能耗降低11%，建筑节能，推广绿色建筑标准（如GBI认证）和智能电网技术； 低 碳交通，电动汽车（EV）推广，目标到2030年EV占新车销量的15%； 提供进口税减免、 充电桩建设补贴等支持； 氢能与碳捕集，目标2030年建成低碳氢中心，2050年成为区域 氢能供应国， 计划2030年前建设3个氢能与碳捕集枢纽， 年储存能力1500万吨； 绿色金融 与投资，2023年设立国家能源转型基金，初始拨款20亿令吉，支持脱碳项目，鼓励私人 资本投资可再生能源和储能项</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="O182" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -14442,14 +14442,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C184" t="n">
         <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
         <v>2</v>
@@ -14477,30 +14477,30 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O184" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
+          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -14517,14 +14517,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C185" t="n">
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
         <v>2</v>
@@ -14552,22 +14552,22 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O185" t="n">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） Publisher: 美国国土安全部（DHS，Federal Register） Country/Jurisdiction: US/CN / Federal Publication date: 2026-08-03 Status: CURRENT Topic: 劳工 Applicability scope: GENERAL Relat</t>
+          <t>Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 Publisher: 联合国商品贸易统计数据库（UN Comtrade） Country/Jurisdiction: US / Federal Publication date: 2026-09-24 Status: CURRENT Topic: 贸易流 Applicability scope: GENERAL Related industries: 动力电池 Key finding: HS 85176</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -14646,7 +14646,7 @@
         </is>
       </c>
       <c r="O186" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         </is>
       </c>
       <c r="O190" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -14967,14 +14967,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C191" t="n">
         <v>5</v>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
         <v>2</v>
@@ -15002,17 +15002,17 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -15021,11 +15021,11 @@
         </is>
       </c>
       <c r="O191" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 Publisher: 特斯拉公司（Tesla, Inc.，SEC EDGAR） Country/Jurisdiction: US/CN/DE / Federal (SEC registrant) Publication date: 2026-01-29 Status: CURRENT Topic: 供应链布局 Applicability scope: GENE</t>
+          <t>Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） Publisher: 商务部 Country/Jurisdiction: CN / National Publication date: 2025-11-09 Status: CURRENT Topic: 出口管制 Applicability scope: GENERAL Related industries: 电池材料 Key finding: 目前仅见第三方转述：暂停期至2026-11-27，涉</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="O195" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="O196" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         </is>
       </c>
       <c r="O197" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="O198" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P198" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         </is>
       </c>
       <c r="O199" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -15642,14 +15642,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C200" t="n">
         <v>4</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
         <v>2</v>
@@ -15677,30 +15677,30 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="O200" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
+          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -15717,14 +15717,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C201" t="n">
         <v>5</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E201" t="n">
         <v>2</v>
@@ -15752,22 +15752,22 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="O201" t="n">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: 美国商务部（经律所解读） Country/Jurisdiction: 柬埔寨/马来西亚/泰国/越南 Publication date: 2023-08-18 Status: CURRENT Topic: 反规避 Applicability scope: GENERAL Related industries: 光伏 Key finding: 2022年4月立案，2023年8月终裁。使用中国组件在东南亚完成的电池和组</t>
+          <t>Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 Publisher: 世界贸易组织（WTO） Country/Jurisdiction: ID / National Publication date: 2020-11-04 Status: CURRENT Topic: 本地化政策 Applicability scope: GENERAL Related industrie</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="O202" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         </is>
       </c>
       <c r="O204" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         </is>
       </c>
       <c r="O207" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P207" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="O210" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="O213" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P213" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003</t>
+          <t>CASE_007; CASE_010; CASE_002; CASE_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -17118,22 +17118,22 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="n">
         <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N3" t="n">
         <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>0.732</v>
+        <v>0.679</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
@@ -17304,40 +17304,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_010</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; CASE_010; DOC_001</t>
+          <t>CASE_002; CASE_003; DOC_001</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="K6" t="n">
         <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.889</v>
+        <v>0.778</v>
       </c>
       <c r="M6" t="n">
         <v>0.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001</t>
+          <t>MOFCOM_002; BIS_002; BIS_001; CASE_009; MOFCOM_001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -17602,7 +17602,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -17706,19 +17706,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_006; CNGOV_001; MOFCOM_004</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1.2</v>
@@ -17730,16 +17730,16 @@
         <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>0.887</v>
+        <v>0.528</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -17788,22 +17788,22 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K13" t="n">
         <v>1.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0.556</v>
+        <v>0.667</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N13" t="n">
         <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0.474</v>
+        <v>0.642</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; NIO_001</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002</t>
+          <t>TRD_001; DHS_001; CASE_003; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -18071,7 +18071,7 @@
         <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.678</v>
+        <v>0.649</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; MOFCOM_003</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; TSLA_001</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -18257,22 +18257,22 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0.741</v>
+        <v>0.799</v>
       </c>
       <c r="P20" t="n">
         <v>1.4</v>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001</t>
+          <t>TRD_003; WH_002; CSIS_001; WTO_001; TRD_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -18339,7 +18339,7 @@
         <v>0.8</v>
       </c>
       <c r="O21" t="n">
-        <v>0.913</v>
+        <v>0.903</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001</t>
+          <t>CSIS_001; CASE_010; USMCA_001; WH_002; WH_001</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -18406,7 +18406,7 @@
         <v>0.8</v>
       </c>
       <c r="O22" t="n">
-        <v>0.903</v>
+        <v>0.887</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001</t>
+          <t>BIS_001; CASE_009; DHS_001; BIS_002; EU_001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -18473,7 +18473,7 @@
         <v>0.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0.792</v>
+        <v>0.766</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -18510,37 +18510,37 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; USMCA_001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; CASE_010; DOC_001; WH_002</t>
+          <t>CASE_002; CASE_003; DOC_001; WH_002</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -18659,22 +18659,22 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N26" t="n">
         <v>0.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.723</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; NIO_001; FR_001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -18726,25 +18726,25 @@
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0.854</v>
+        <v>0.903</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -18845,12 +18845,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003</t>
+          <t>TRD_003; CASE_002; WH_002; DOC_001; CASE_010</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; CASE_010; TRD_003; WH_002</t>
+          <t>CASE_002; CASE_010; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -18860,22 +18860,22 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.854</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001</t>
+          <t>WTO_001; WTO_002; IMF_001; CNGOV_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -18942,7 +18942,7 @@
         <v>0.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0.616</v>
+        <v>0.447</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -18994,22 +18994,22 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0.741</v>
+        <v>0.79</v>
       </c>
       <c r="P31" t="n">
         <v>1.8</v>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001</t>
+          <t>ALB_001; DHS_001; SNE_001; TRD_001; EU_003</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -19195,22 +19195,22 @@
         <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K34" t="n">
         <v>1.2</v>
       </c>
       <c r="L34" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.872</v>
+        <v>0.794</v>
       </c>
       <c r="P34" t="n">
         <v>1.8</v>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004</t>
+          <t>WTO_002; WTO_003; IRS_001; WTO_004; DHS_001</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001</t>
+          <t>WTO_004; IRS_001; DHS_001; EU_001; MOFCOM_004</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -19396,25 +19396,25 @@
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K37" t="n">
         <v>1.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.872</v>
+        <v>0.821</v>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WB_001; CASE_002; TRD_001; DHS_001; EU_003</t>
+          <t>WB_001; CASE_002; DHS_001; TRD_001; EU_003</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -19478,7 +19478,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.707</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="P38" t="n">
         <v>2</v>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -19530,22 +19530,22 @@
         <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K39" t="n">
         <v>1.2</v>
       </c>
       <c r="L39" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.771</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="P39" t="n">
         <v>1.8</v>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002</t>
+          <t>USMCA_001; WB_001; IRS_001; CASE_002; WTO_004</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -19679,7 +19679,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.858</v>
+        <v>0.84</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
